--- a/results/Consolidated_Metrics.xlsx
+++ b/results/Consolidated_Metrics.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/balajivenktesh/Desktop/Education/Docstring_RAG/RAG-Docstring/results/Llama-3-8B/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/balajivenktesh/Desktop/Education/Docstring_RAG/RAG-Docstring/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0310AD-1212-2E4A-8037-B73157FC4AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646746D9-A78E-564F-876C-197077886722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{74EED66A-0D25-D54C-9E90-E67CE61EDA5A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Metrics" sheetId="1" r:id="rId1"/>
+    <sheet name="bkp" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="33">
   <si>
     <t>rouge_1_f1</t>
   </si>
@@ -118,6 +120,24 @@
   <si>
     <t>Qwen</t>
   </si>
+  <si>
+    <t>plain</t>
+  </si>
+  <si>
+    <t>got</t>
+  </si>
+  <si>
+    <t>cot</t>
+  </si>
+  <si>
+    <t>tot</t>
+  </si>
+  <si>
+    <t>got rag</t>
+  </si>
+  <si>
+    <t>cot self</t>
+  </si>
 </sst>
 </file>
 
@@ -126,7 +146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -135,22 +155,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -188,18 +203,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7E8038-72A1-D646-A114-988FEA4EA1D2}">
-  <dimension ref="A4:X56"/>
+  <dimension ref="A3:X56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -553,57 +565,57 @@
     <col min="17" max="17" width="18.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Q5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -611,660 +623,660 @@
       <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3">
-        <v>0.19044825700387852</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1.0027454631606167E-2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.5951829125632101</v>
-      </c>
-      <c r="F6" s="3">
-        <v>47.400635200510258</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.82769651788176246</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.52774703956661817</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.92537313432835822</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0.79104477611940294</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.501</v>
-      </c>
-      <c r="L6" s="3">
-        <v>7.4440167092565277</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1672.4388992537313</v>
-      </c>
-      <c r="N6" s="3">
-        <v>10.386567164179105</v>
-      </c>
-      <c r="O6" s="3">
+      <c r="C6" s="2">
+        <v>0.13233463072057258</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.9124737354638552E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.57001682270818677</v>
+      </c>
+      <c r="F6" s="2">
+        <v>34.185824577069148</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.41573777296415698</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.44695754471180754</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.97014925373134331</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.91044776119402981</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0.73671641791044784</v>
+      </c>
+      <c r="L6" s="2">
+        <v>4.9327374892448317</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1138.3538945895523</v>
+      </c>
+      <c r="N6" s="2">
+        <v>11.580597014925372</v>
+      </c>
+      <c r="O6" s="2">
         <v>1</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>0</v>
       </c>
-      <c r="Q6" s="3">
-        <v>7.4440141613803696</v>
+      <c r="Q6" s="2">
+        <v>4.93273508726661</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3">
-        <v>0.19142592389083304</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6.5674980394216315E-3</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.6017481400005853</v>
-      </c>
-      <c r="F7" s="3">
-        <v>38.143393623214294</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.79561270240213067</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.56300606736064907</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.86567164179104472</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.78358208955223885</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L7" s="3">
-        <v>7.0538341963469096</v>
-      </c>
-      <c r="M7" s="3">
-        <v>2153.53125</v>
-      </c>
-      <c r="N7" s="3">
-        <v>10.400000000000004</v>
-      </c>
-      <c r="O7" s="3">
+      <c r="C7" s="2">
+        <v>0.12491715789713849</v>
+      </c>
+      <c r="D7" s="2">
+        <v>5.9972077862933981E-4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.57207663824309163</v>
+      </c>
+      <c r="F7" s="2">
+        <v>34.95224986511198</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.41427179766315081</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.42421756795745985</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.95522388059701491</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.97014925373134331</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.7201492537313432</v>
+      </c>
+      <c r="L7" s="2">
+        <v>3.1718558517854607</v>
+      </c>
+      <c r="M7" s="2">
+        <v>1122.6031949626865</v>
+      </c>
+      <c r="N7" s="2">
+        <v>11.450746268656721</v>
+      </c>
+      <c r="O7" s="2">
         <v>1</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="2">
         <v>0</v>
       </c>
-      <c r="Q7" s="3">
-        <v>7.0538318228365773</v>
+      <c r="Q7" s="2">
+        <v>3.1718539408783415</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="3">
-        <v>0.2114569761579029</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1.0628572072660328E-2</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.58059626639778938</v>
-      </c>
-      <c r="F8" s="3">
-        <v>44.525437060275692</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1.208701986315271</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.46281507854159293</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0.82089552238805974</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0.67848258706467657</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0.504</v>
-      </c>
-      <c r="L8" s="3">
-        <v>21.933837502749999</v>
-      </c>
-      <c r="M8" s="3">
-        <v>2153.5390625</v>
-      </c>
-      <c r="N8" s="3">
-        <v>10.510447761194031</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="C8" s="2">
+        <v>0.17163672592288029</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.9184232126111742E-3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.55730550547144309</v>
+      </c>
+      <c r="F8" s="2">
+        <v>32.237345522176284</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1.2312874257076516</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.4536468667545096</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.97014925373134331</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.67723880597014929</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0.6892537313432836</v>
+      </c>
+      <c r="L8" s="2">
+        <v>29.667150935130334</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1123.844916044776</v>
+      </c>
+      <c r="N8" s="2">
+        <v>11.580597014925374</v>
+      </c>
+      <c r="O8" s="2">
+        <v>5</v>
+      </c>
+      <c r="P8" s="2">
         <v>0</v>
       </c>
-      <c r="Q8" s="3">
-        <v>21.933835246669712</v>
+      <c r="Q8" s="2">
+        <v>29.667148878325278</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="4">
-        <v>0.20948458860386041</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1.2278276277266494E-2</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0.58063720233404814</v>
-      </c>
-      <c r="F9" s="3">
-        <v>49.563489766555115</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0.89499915528404284</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.37921446138025777</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0.74626865671641796</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.70335820895522383</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0.502</v>
-      </c>
-      <c r="L9" s="3">
-        <v>74.48768618925294</v>
-      </c>
-      <c r="M9" s="3">
-        <v>2167.0234375</v>
-      </c>
-      <c r="N9" s="3">
-        <v>10.526865671641797</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="C9" s="2">
+        <v>0.16770139518644961</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3.8595135772878327E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.55139082180919929</v>
+      </c>
+      <c r="F9" s="2">
+        <v>37.149684636003947</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.94544240769610888</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.44300645976689129</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0.53731343283582089</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.55970149253731338</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.78611940298507477</v>
+      </c>
+      <c r="L9" s="2">
+        <v>63.878905186012609</v>
+      </c>
+      <c r="M9" s="2">
+        <v>1123.5100862873135</v>
+      </c>
+      <c r="N9" s="2">
+        <v>11.397014925373133</v>
+      </c>
+      <c r="O9" s="2">
+        <v>20</v>
+      </c>
+      <c r="P9" s="2">
         <v>0</v>
       </c>
-      <c r="Q9" s="3">
-        <v>74.487683456335489</v>
+      <c r="Q9" s="2">
+        <v>63.878902858762601</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>0.19994465240252654</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>5.9560246404671254E-3</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>0.59772271674070787</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>39.951834138885204</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>0.7053079351965843</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>0.45451281931516202</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>0.94029850746268662</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>0.84514925373134331</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <v>0.73134328358208922</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>5.8977674192457057</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <v>1960.5428521455224</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <v>10.546268656716419</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="2">
         <v>2</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="2">
         <v>5.3712848407119068E-2</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="2">
         <v>5.844051699140179</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>0.17545214136309037</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>8.4873868822894407E-3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>0.57418376718884079</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>32.926303684983736</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>0.64169908235550621</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <v>0.48913354684633736</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <v>0.74626865671641796</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <v>0.66417910447761197</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="2">
         <v>0.70149253731343253</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="2">
         <v>8.6867375195916026</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="2">
         <v>2113.7776935634329</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="2">
         <v>10.520895522388059</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="2">
         <v>2</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="2">
         <v>4.9725657078757216E-2</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="2">
         <v>8.6370079873213133</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>0.204735656074085</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>7.584399736661457E-3</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>0.5789411623976124</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>42.857727852042942</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>1.0415996685547879</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <v>0.42771944693990799</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <v>0.89552238805970152</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <v>0.6983830845771144</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="2">
         <v>0.59552238805970148</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="2">
         <v>24.741841487030484</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="2">
         <v>2151.62109375</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="2">
         <v>10.638805970149257</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="2">
         <v>2</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="2">
         <v>5.9200927392760318E-2</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="2">
         <v>24.68263666665376</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>0.20502769198523318</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>1.1784305247467619E-2</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>0.58622122656053577</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>44.722038885863107</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>0.85686959597510182</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <v>0.47088177400027587</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <v>0.65671641791044777</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <v>0.6393034825870646</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="2">
         <v>0.63432835820895528</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="2">
         <v>89.516627379317782</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="2">
         <v>2135.1328125</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="2">
         <v>10.55223880597015</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="2">
         <v>2</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="2">
         <v>0.28309739881487034</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="2">
         <v>89.233526201390504</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>0.20339808627570219</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>8.9795522015474073E-3</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>0.5690343704686236</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>50.67575136613452</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>0.71823784277418423</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <v>0.28716791663224361</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <v>0.61194029850746268</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="2">
         <v>0.64925373134328357</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="2">
         <v>0.57313432835820899</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="2">
         <v>8.82217402956379</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="2">
         <v>1950.1653451492537</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="2">
         <v>10.840298507462686</v>
       </c>
-      <c r="O16" s="3">
+      <c r="O16" s="2">
         <v>2.6567164179104479</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="2">
         <v>0.15025633840418573</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="Q16" s="2">
         <v>6.6097579892001939</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>0.20414657886227325</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>7.7619949061558426E-3</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>0.56207129981980397</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>48.865240319554644</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>0.68485815776467462</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <v>0.27366497028481224</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <v>0.5074626865671642</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="2">
         <v>0.53917910447761197</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="2">
         <v>0.57164179104477608</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="2">
         <v>9.8907122825508687</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="2">
         <v>2168.3054454291046</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="2">
         <v>10.616417910447765</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="2">
         <v>2.7462686567164178</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="2">
         <v>0.2041642594693312</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="2">
         <v>6.6563290944739952</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>0.22130817902676686</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>5.8402049129197449E-3</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>0.58526452441713706</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>50.704428888141692</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>0.69985367000891319</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <v>0.40788228786241809</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <v>0.64179104477611937</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="2">
         <v>0.63059701492537312</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="2">
         <v>0.5432835820895523</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="2">
         <v>22.207262651244207</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="2">
         <v>2218.3671875</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="2">
         <v>10.602985074626867</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="2">
         <v>2.7462686567164178</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="2">
         <v>0.14772969217442755</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="2">
         <v>12.115700348099665</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>0.19503571286973959</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>4.7286883369824836E-3</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>0.55974105845636402</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>47.295797618047239</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>0.54261826870947838</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <v>0.26735269746452223</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="2">
         <v>0.55223880597014929</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <v>0.55970149253731338</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19" s="2">
         <v>0.5223880597014926</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="2">
         <v>50.279314357842971</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M19" s="2">
         <v>2191.4255480410447</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="2">
         <v>10.588059701492535</v>
       </c>
-      <c r="O19" s="3">
+      <c r="O19" s="2">
         <v>2.6865671641791047</v>
       </c>
-      <c r="P19" s="3">
+      <c r="P19" s="2">
         <v>0.28949160718206152</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="Q19" s="2">
         <v>12.053952868305036</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1272,667 +1284,667 @@
       <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="3">
-        <v>0.17187122778704217</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1.6823359327930115E-3</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0.53625104943318158</v>
-      </c>
-      <c r="F24" s="3">
-        <v>33.017458358980285</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1.2965315430118054</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0.36585734129401243</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0.52238805970149249</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0.77272727272727271</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="3">
-        <v>6.5443769141809263</v>
-      </c>
-      <c r="M24" s="3">
-        <v>1676.9828591417911</v>
-      </c>
-      <c r="N24" s="3">
-        <v>10.508955223880601</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="C24" s="2">
+        <v>6.545635018463597E-2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1.1133412201131752E-3</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.39599833670836776</v>
+      </c>
+      <c r="F24" s="2">
+        <v>16.636197735410072</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.73919516882870817</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.17542487144111377</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0.38805970149253732</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.60895522388059697</v>
+      </c>
+      <c r="L24" s="2">
+        <v>32.887150938831155</v>
+      </c>
+      <c r="M24" s="2">
+        <v>1122.8927821828358</v>
+      </c>
+      <c r="N24" s="2">
+        <v>10.779104477611938</v>
+      </c>
+      <c r="O24" s="2">
         <v>1</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="2">
         <v>0</v>
       </c>
-      <c r="Q24" s="3">
-        <v>6.5443749392210551</v>
+      <c r="Q24" s="2">
+        <v>32.887148778830003</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="3">
-        <v>0.17801849367442651</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2.5685541088484817E-3</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0.54878822680729533</v>
-      </c>
-      <c r="F25" s="3">
-        <v>32.842687163703374</v>
-      </c>
-      <c r="G25" s="3">
-        <v>1.4169761380514467</v>
-      </c>
-      <c r="H25" s="3">
-        <v>0.44444235405605026</v>
-      </c>
-      <c r="I25" s="3">
-        <v>0.53731343283582089</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0.73484848484848486</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L25" s="3">
-        <v>9.075428215425406</v>
-      </c>
-      <c r="M25" s="3">
-        <v>2145.71484375</v>
-      </c>
-      <c r="N25" s="3">
-        <v>10.620895522388061</v>
-      </c>
-      <c r="O25" s="3">
+      <c r="C25" s="2">
+        <v>6.4359140320740096E-2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>6.7433027573594981E-4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.43765674042167946</v>
+      </c>
+      <c r="F25" s="2">
+        <v>56.1713740072382</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0.86771694692721235</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0.10024875621890546</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0.19402985074626866</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0.47761194029850745</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0.51517412935323381</v>
+      </c>
+      <c r="L25" s="2">
+        <v>12.547144968118241</v>
+      </c>
+      <c r="M25" s="2">
+        <v>1087.5989972014925</v>
+      </c>
+      <c r="N25" s="2">
+        <v>11.505970149253733</v>
+      </c>
+      <c r="O25" s="2">
         <v>1</v>
       </c>
-      <c r="P25" s="3">
+      <c r="P25" s="2">
         <v>0</v>
       </c>
-      <c r="Q25" s="3">
-        <v>9.0754260376318179</v>
+      <c r="Q25" s="2">
+        <v>12.547143114146902</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="3">
-        <v>6.393939405995154E-2</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1.1433550834854814E-80</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0.37233568816932278</v>
-      </c>
-      <c r="F26" s="3">
-        <v>41.504495545278353</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0.59577970437119787</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1.5991471215351813E-2</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0.13432835820895522</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0.45614035087719296</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L26" s="3">
-        <v>31.539145391378831</v>
-      </c>
-      <c r="M26" s="3">
-        <v>2180.40234375</v>
-      </c>
-      <c r="N26" s="3">
-        <v>10.561194029850748</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="C26" s="2">
+        <v>0.10887106917037502</v>
+      </c>
+      <c r="D26" s="2">
+        <v>5.8409831720597786E-4</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.50454291212024971</v>
+      </c>
+      <c r="F26" s="2">
+        <v>35.699222830410498</v>
+      </c>
+      <c r="G26" s="2">
+        <v>5.5133439772955581</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0.2351066003063369</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0.34328358208955223</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0.59888059701492535</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="L26" s="2">
+        <v>72.249147404485669</v>
+      </c>
+      <c r="M26" s="2">
+        <v>1124.1605643656717</v>
+      </c>
+      <c r="N26" s="2">
+        <v>11.402985074626866</v>
+      </c>
+      <c r="O26" s="2">
         <v>5</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="2">
         <v>0</v>
       </c>
-      <c r="Q26" s="3">
-        <v>31.539142669136844</v>
+      <c r="Q26" s="2">
+        <v>72.249145027416859</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="3">
-        <v>6.2242148159929879E-2</v>
-      </c>
-      <c r="D27" s="3">
-        <v>5.7848736720451813E-4</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0.36754202531344854</v>
-      </c>
-      <c r="F27" s="3">
-        <v>30.597357698410029</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0.55069848681965272</v>
-      </c>
-      <c r="H27" s="3">
-        <v>5.3980099502487562E-2</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="C27" s="2">
+        <v>3.2366258613803003E-2</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3.863700800493757E-5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.31777023735331067</v>
+      </c>
+      <c r="F27" s="2">
+        <v>18.796328645593785</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.64484053375843819</v>
+      </c>
+      <c r="H27" s="2">
+        <v>3.3582089552238806E-2</v>
+      </c>
+      <c r="I27" s="2">
         <v>0.16417910447761194</v>
       </c>
-      <c r="J27" s="3">
-        <v>0.44642857142857145</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L27" s="3">
-        <v>50.368515954088807</v>
-      </c>
-      <c r="M27" s="3">
-        <v>2180.3982042910447</v>
-      </c>
-      <c r="N27" s="3">
-        <v>10.632835820895526</v>
-      </c>
-      <c r="O27" s="3">
-        <v>19.985074626865671</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="J27" s="2">
+        <v>0.44711538461538464</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.55567164179104489</v>
+      </c>
+      <c r="L27" s="2">
+        <v>101.17893225755265</v>
+      </c>
+      <c r="M27" s="2">
+        <v>1075.634911380597</v>
+      </c>
+      <c r="N27" s="2">
+        <v>11.229850746268662</v>
+      </c>
+      <c r="O27" s="2">
+        <v>19.970149253731343</v>
+      </c>
+      <c r="P27" s="2">
         <v>0</v>
       </c>
-      <c r="Q27" s="3">
-        <v>50.368513292341092</v>
+      <c r="Q27" s="2">
+        <v>101.17893029326824</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="2">
         <v>7.4357338638124423E-2</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="2">
         <v>2.8599389235983896E-80</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="2">
         <v>0.40856845765861111</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>42.375282118241429</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="2">
         <v>0.78333346135989057</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="2">
         <v>6.3868159203980104E-2</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="2">
         <v>0.20895522388059701</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="2">
         <v>0.515625</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="2">
         <v>0.62313432835820892</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="2">
         <v>15.75743283442597</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="2">
         <v>1981.6038945895523</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="2">
         <v>10.317910447761193</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="2">
         <v>0</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="2">
         <v>0.29235350907738528</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="2">
         <v>15.757432830000001</v>
       </c>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
-      <c r="X29" s="6"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="3">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3">
-        <v>7.1640874461814802E-2</v>
-      </c>
-      <c r="H30" s="3">
-        <v>1.4925373134328358E-2</v>
-      </c>
-      <c r="I30" s="3">
-        <v>0.13432835820895522</v>
-      </c>
-      <c r="J30" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L30" s="3">
-        <v>12.968025908541323</v>
-      </c>
-      <c r="M30" s="3">
-        <v>2176.3671875</v>
-      </c>
-      <c r="N30" s="3">
-        <v>10.12537313432836</v>
-      </c>
-      <c r="O30" s="3">
-        <v>1</v>
-      </c>
-      <c r="P30" s="3">
-        <v>0.28468015300693794</v>
-      </c>
-      <c r="Q30" s="3">
-        <v>12.683343143605475</v>
+      <c r="C30" s="2">
+        <v>6.0056694885999795E-2</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3.7402823509720762E-5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0.40375139997966253</v>
+      </c>
+      <c r="F30" s="2">
+        <v>54.251200854475535</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.60507362844870649</v>
+      </c>
+      <c r="H30" s="2">
+        <v>5.9914712153518124E-2</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.14925373134328357</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0.47692307692307695</v>
+      </c>
+      <c r="K30" s="2">
+        <v>0.80820895522388059</v>
+      </c>
+      <c r="L30" s="2">
+        <v>15.530315221245608</v>
+      </c>
+      <c r="M30" s="2">
+        <v>1365.955865205224</v>
+      </c>
+      <c r="N30" s="2">
+        <v>10.994029850746266</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="P30" s="2">
+        <v>0.11806695141009431</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>15.41224577533665</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="3">
-        <v>0.1233510643546198</v>
-      </c>
-      <c r="D31" s="3">
-        <v>1.2355006219312719E-3</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0.47611352489955389</v>
-      </c>
-      <c r="F31" s="3">
-        <v>29.787574661182045</v>
-      </c>
-      <c r="G31" s="3">
-        <v>1.5859703495953432</v>
-      </c>
-      <c r="H31" s="3">
-        <v>0.25565442142483413</v>
-      </c>
-      <c r="I31" s="3">
-        <v>0.40298507462686567</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="K31" s="3">
-        <v>1.7992537313432835</v>
-      </c>
-      <c r="L31" s="3">
-        <v>43.254507648411085</v>
-      </c>
-      <c r="M31" s="3">
-        <v>2260.4869986007461</v>
-      </c>
-      <c r="N31" s="3">
-        <v>10.47313432835821</v>
-      </c>
-      <c r="O31" s="3">
+      <c r="C31" s="2">
+        <v>6.7803869353453936E-2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>4.070790554585057E-4</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.42696540902799635</v>
+      </c>
+      <c r="F31" s="2">
+        <v>52.381051688795914</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.86457838519625596</v>
+      </c>
+      <c r="H31" s="2">
+        <v>8.9054726368159212E-2</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0.17910447761194029</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.47692307692307695</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0.87611940298507451</v>
+      </c>
+      <c r="L31" s="2">
+        <v>58.184971784477803</v>
+      </c>
+      <c r="M31" s="2">
+        <v>1367.4007695895523</v>
+      </c>
+      <c r="N31" s="2">
+        <v>11.173134328358206</v>
+      </c>
+      <c r="O31" s="2">
         <v>5</v>
       </c>
-      <c r="P31" s="3">
-        <v>0.31781011552953009</v>
-      </c>
-      <c r="Q31" s="3">
-        <v>42.936694746586817</v>
+      <c r="P31" s="2">
+        <v>0.14740811888851338</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>58.037561128388589</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>8.1073729927789204E-2</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="2">
         <v>1.571567766309332E-80</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>0.42060439177413483</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>41.726882280440613</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="2">
         <v>0.58251703380657316</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <v>4.3319118692253022E-2</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="2">
         <v>0.14925373134328357</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="2">
         <v>0.4838709677419355</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="2">
         <v>0.64350746268656711</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="2">
         <v>76.351359296200883</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="2">
         <v>2203.453125</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="2">
         <v>10.374626865671637</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="2">
         <v>19.671641791044777</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="2">
         <v>0.69744205830702144</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="2">
         <v>75.653914181154164</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="2">
         <v>0.18353222761234828</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="2">
         <v>1.7122495972315774E-3</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="2">
         <v>0.55960627456209555</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
         <v>27.318773876372692</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="2">
         <v>0.97568072988664178</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="2">
         <v>0.49396904028101751</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="2">
         <v>0.5074626865671642</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="2">
         <v>0.65671641791044777</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="2">
         <v>0.58283582089552233</v>
       </c>
-      <c r="L34" s="3">
+      <c r="L34" s="2">
         <v>37.424903595625466</v>
       </c>
-      <c r="M34" s="3">
+      <c r="M34" s="2">
         <v>1946.1343866604477</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34" s="2">
         <v>9.8611940298507452</v>
       </c>
-      <c r="O34" s="3">
+      <c r="O34" s="2">
         <v>3.4029850746268657</v>
       </c>
-      <c r="P34" s="3">
+      <c r="P34" s="2">
         <v>1.6870921263054235</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="Q34" s="2">
         <v>24.93746585632438</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="2">
         <v>8.5884344168582261E-2</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="2">
         <v>5.936586581684919E-5</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="2">
         <v>0.4180413715874971</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>33.967473243603955</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="2">
         <v>0.94675389136477706</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="2">
         <v>6.7501776830135043E-2</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="2">
         <v>0.19402985074626866</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="2">
         <v>0.50403225806451613</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="2">
         <v>0.63805970149253732</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="2">
         <v>25.561154290811338</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="2">
         <v>2120.96875</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="2">
         <v>9.6417910447761201</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="2">
         <v>3.5223880597014925</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="2">
         <v>1.9421251033669087</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="2">
         <v>11.508546096175465</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="2">
         <v>7.9005577236416213E-2</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="2">
         <v>1.7117909315242128E-80</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="2">
         <v>0.38339155556550669</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>32.912814419268088</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="2">
         <v>0.87750061645277477</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="2">
         <v>4.4527363184079606E-2</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="2">
         <v>0.17910447761194029</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="2">
         <v>0.46666666666666667</v>
       </c>
-      <c r="K36" s="3">
+      <c r="K36" s="2">
         <v>0.60149253731343277</v>
       </c>
-      <c r="L36" s="3">
+      <c r="L36" s="2">
         <v>44.033866451747379</v>
       </c>
-      <c r="M36" s="3">
+      <c r="M36" s="2">
         <v>2164.8579174440297</v>
       </c>
-      <c r="N36" s="3">
+      <c r="N36" s="2">
         <v>10.38208955223881</v>
       </c>
-      <c r="O36" s="3">
+      <c r="O36" s="2">
         <v>3.5522388059701493</v>
       </c>
-      <c r="P36" s="3">
+      <c r="P36" s="2">
         <v>0.60724402185696269</v>
       </c>
-      <c r="Q36" s="3">
+      <c r="Q36" s="2">
         <v>9.9746443905047517</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="2">
         <v>7.2651468633059546E-2</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="2">
         <v>1.7821950214249403E-4</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="2">
         <v>0.37483565709484157</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>31.86824809127102</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="2">
         <v>0.58580871747687857</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="2">
         <v>3.4825870646766163E-2</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="2">
         <v>0.14925373134328357</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="2">
         <v>0.48214285714285715</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="2">
         <v>0.57164179104477608</v>
       </c>
-      <c r="L37" s="3">
+      <c r="L37" s="2">
         <v>72.780948670942394</v>
       </c>
-      <c r="M37" s="3">
+      <c r="M37" s="2">
         <v>2149.73046875</v>
       </c>
-      <c r="N37" s="3">
+      <c r="N37" s="2">
         <v>10.329850746268658</v>
       </c>
-      <c r="O37" s="3">
+      <c r="O37" s="2">
         <v>3.6716417910447761</v>
       </c>
-      <c r="P37" s="3">
+      <c r="P37" s="2">
         <v>1.4789056493275201</v>
       </c>
-      <c r="Q37" s="3">
+      <c r="Q37" s="2">
         <v>7.0157200222584741</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="A40" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1940,655 +1952,655 @@
       <c r="A43" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C43" s="3">
-        <v>0.22905068022933589</v>
-      </c>
-      <c r="D43" s="3">
-        <v>1.1152577439444446E-2</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0.61808595550594048</v>
-      </c>
-      <c r="F43" s="3">
-        <v>45.598096434646877</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0.95546021069836251</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0.62998481367838144</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0.95522388059701491</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0.96268656716417911</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L43" s="3">
-        <v>14.424395102173534</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1670.2953008395523</v>
-      </c>
-      <c r="N43" s="3">
-        <v>14.038805970149252</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="C43" s="2">
+        <v>0.21530080936202481</v>
+      </c>
+      <c r="D43" s="2">
+        <v>6.6622678418142801E-3</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.61038548110136348</v>
+      </c>
+      <c r="F43" s="2">
+        <v>42.735642216257276</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.85546375302721889</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0.53527463986141943</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0.94776119402985071</v>
+      </c>
+      <c r="K43" s="2">
+        <v>0.75074626865671645</v>
+      </c>
+      <c r="L43" s="2">
+        <v>15.28755542769361</v>
+      </c>
+      <c r="M43" s="2">
+        <v>1122.0673973880596</v>
+      </c>
+      <c r="N43" s="2">
+        <v>14.408955223880595</v>
+      </c>
+      <c r="O43" s="2">
         <v>1</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="2">
         <v>0</v>
       </c>
-      <c r="Q43" s="3">
-        <v>14.424392885236598</v>
+      <c r="Q43" s="2">
+        <v>15.287553498994059</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="3">
-        <v>0.2021592012386858</v>
-      </c>
-      <c r="D44" s="3">
-        <v>6.5812006295377116E-3</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0.6112028956413269</v>
-      </c>
-      <c r="F44" s="3">
-        <v>39.85652053554788</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0.86298285713829903</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0.64132707773771014</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="C44" s="2">
+        <v>0.19594166323331214</v>
+      </c>
+      <c r="D44" s="2">
+        <v>6.8031551320158964E-3</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.61454447214283159</v>
+      </c>
+      <c r="F44" s="2">
+        <v>36.259692072827669</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0.78365906993502765</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0.64154805379506175</v>
+      </c>
+      <c r="I44" s="2">
         <v>0.9850746268656716</v>
       </c>
-      <c r="J44" s="3">
-        <v>0.94402985074626866</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L44" s="3">
-        <v>20.294896631098506</v>
-      </c>
-      <c r="M44" s="3">
-        <v>2157.7109375</v>
-      </c>
-      <c r="N44" s="3">
-        <v>13.992537313432834</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="J44" s="2">
+        <v>0.97014925373134331</v>
+      </c>
+      <c r="K44" s="2">
+        <v>0.77611940298507465</v>
+      </c>
+      <c r="L44" s="2">
+        <v>12.815101360207173</v>
+      </c>
+      <c r="M44" s="2">
+        <v>1122.8698111007463</v>
+      </c>
+      <c r="N44" s="2">
+        <v>14.476119402985072</v>
+      </c>
+      <c r="O44" s="2">
         <v>1</v>
       </c>
-      <c r="P44" s="3">
+      <c r="P44" s="2">
         <v>0</v>
       </c>
-      <c r="Q44" s="3">
-        <v>20.294893908856519</v>
+      <c r="Q44" s="2">
+        <v>12.81509926425877</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="5"/>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C45" s="3">
-        <v>0.19737082006448006</v>
-      </c>
-      <c r="D45" s="3">
-        <v>4.6299999999999996E-3</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0.58431</v>
-      </c>
-      <c r="F45" s="3">
-        <v>26.606400000000001</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1.083974</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0.48241200000000001</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0.82089599999999996</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0.74813399999999997</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L45" s="3">
-        <v>40.78233310357848</v>
-      </c>
-      <c r="M45" s="3">
-        <v>2210.234375</v>
-      </c>
-      <c r="N45" s="3">
-        <v>11.650746268656714</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="C45" s="2">
+        <v>0.19406970237595625</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2.4203450836149092E-3</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.58861867438501392</v>
+      </c>
+      <c r="F45" s="2">
+        <v>25.943232599275586</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1.0785077163649486</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0.55571408667730471</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0.83582089552238803</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0.72139303482587058</v>
+      </c>
+      <c r="K45" s="2">
+        <v>0.77611940298507465</v>
+      </c>
+      <c r="L45" s="2">
+        <v>39.865547792235418</v>
+      </c>
+      <c r="M45" s="2">
+        <v>1122.2135027985075</v>
+      </c>
+      <c r="N45" s="2">
+        <v>12.153731343283585</v>
+      </c>
+      <c r="O45" s="2">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="2">
         <v>0</v>
       </c>
-      <c r="Q45" s="3">
-        <v>40.782330456064706</v>
+      <c r="Q45" s="2">
+        <v>39.865545639351232</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="5"/>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="3">
-        <v>0.20369947755337284</v>
-      </c>
-      <c r="D46" s="3">
-        <v>9.1450236014765547E-3</v>
-      </c>
-      <c r="E46" s="3">
-        <v>0.59539986679803081</v>
-      </c>
-      <c r="F46" s="3">
-        <v>31.721091955655531</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1.0026481370546769</v>
-      </c>
-      <c r="H46" s="3">
-        <v>0.4466487023288927</v>
-      </c>
-      <c r="I46" s="3">
-        <v>0.44776119402985076</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0.53917910447761197</v>
-      </c>
-      <c r="K46" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L46" s="3">
-        <v>159.84443189137016</v>
-      </c>
-      <c r="M46" s="3">
-        <v>2208.078125</v>
-      </c>
-      <c r="N46" s="3">
-        <v>13.268656716417905</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="C46" s="2">
+        <v>0.2114148882347176</v>
+      </c>
+      <c r="D46" s="2">
+        <v>7.0747174143504848E-3</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.60394656791615842</v>
+      </c>
+      <c r="F46" s="2">
+        <v>31.131736170980155</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1.1030699196685489</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0.56443475364389351</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0.47761194029850745</v>
+      </c>
+      <c r="J46" s="2">
+        <v>0.55783582089552242</v>
+      </c>
+      <c r="K46" s="2">
+        <v>0.77537313432835808</v>
+      </c>
+      <c r="L46" s="2">
+        <v>150.78266205004792</v>
+      </c>
+      <c r="M46" s="2">
+        <v>1122.27734375</v>
+      </c>
+      <c r="N46" s="2">
+        <v>13.683582089552246</v>
+      </c>
+      <c r="O46" s="2">
         <v>20</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="2">
         <v>0</v>
       </c>
-      <c r="Q46" s="3">
-        <v>159.84442842540457</v>
+      <c r="Q46" s="2">
+        <v>150.78265983666947</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="2">
         <v>0.20881812551821424</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="2">
         <v>7.3598419939542199E-3</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="2">
         <v>0.61176689035856902</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="2">
         <v>38.375805265195865</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="2">
         <v>0.90488087818980123</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="2">
         <v>0.63751482358755585</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="2">
         <v>0.91044776119402981</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="2">
         <v>0.89925373134328357</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="2">
         <v>0.68582089552238812</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="2">
         <v>28.177562090887953</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="2">
         <v>1436.3000816231342</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="2">
         <v>13.020895522388061</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="2">
         <v>0</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="2">
         <v>0.32969876189730063</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="2">
         <v>27.847860738412656</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="5"/>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="3">
-        <v>0</v>
-      </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>7.1640874461814802E-2</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1.4925373134328358E-2</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0.13432835820895522</v>
-      </c>
-      <c r="J49" s="3" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="L49" s="3">
-        <v>11.426206343209564</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1421.2271455223881</v>
-      </c>
-      <c r="N49" s="3">
-        <v>10.698507462686566</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="C49" s="2">
+        <v>0.17937367748902555</v>
+      </c>
+      <c r="D49" s="2">
+        <v>3.8740218468176894E-3</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0.59161838889122009</v>
+      </c>
+      <c r="F49" s="2">
+        <v>35.761200906390499</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0.68449008652025978</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0.54354677849144362</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0.95522388059701491</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0.97014925373134331</v>
+      </c>
+      <c r="K49" s="2">
+        <v>0.88864179104477625</v>
+      </c>
+      <c r="L49" s="2">
+        <v>22.700881612834646</v>
+      </c>
+      <c r="M49" s="2">
+        <v>1438.498192630597</v>
+      </c>
+      <c r="N49" s="2">
+        <v>13.401492537313436</v>
+      </c>
+      <c r="O49" s="2">
         <v>1</v>
       </c>
-      <c r="P49" s="3">
-        <v>0.28546695922737692</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>11.140736889483323</v>
+      <c r="P49" s="2">
+        <v>7.1907431332033075E-2</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>22.628971633626453</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="5"/>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="2">
         <v>0.19852939963250166</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="2">
         <v>3.996524308071102E-3</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="2">
         <v>0.58518743025722786</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="2">
         <v>25.751766564098752</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="2">
         <v>1.0394785720335886</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="2">
         <v>0.52600114434595291</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I50" s="2">
         <v>0.83582089552238803</v>
       </c>
-      <c r="J50" s="3">
+      <c r="J50" s="2">
         <v>0.73320895522388063</v>
       </c>
-      <c r="K50" s="3">
+      <c r="K50" s="2">
         <v>0.7638805970149255</v>
       </c>
-      <c r="L50" s="3">
+      <c r="L50" s="2">
         <v>57.103537947384282</v>
       </c>
-      <c r="M50" s="3">
+      <c r="M50" s="2">
         <v>1438.3797224813434</v>
       </c>
-      <c r="N50" s="3">
+      <c r="N50" s="2">
         <v>11.8</v>
       </c>
-      <c r="O50" s="3">
+      <c r="O50" s="2">
         <v>5</v>
       </c>
-      <c r="P50" s="3">
+      <c r="P50" s="2">
         <v>0.11977350178049571</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="Q50" s="2">
         <v>56.983761815882438</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="5"/>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="2">
         <v>0.21584857273268659</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="2">
         <v>1.3672712887557373E-2</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="2">
         <v>0.59885577523886269</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="2">
         <v>35.832311265980614</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="2">
         <v>1.1132990820283772</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="2">
         <v>0.55255363446528372</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I51" s="2">
         <v>0.62686567164179108</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J51" s="2">
         <v>0.62873134328358204</v>
       </c>
-      <c r="K51" s="3">
+      <c r="K51" s="2">
         <v>0.68358208955223887</v>
       </c>
-      <c r="L51" s="3">
+      <c r="L51" s="2">
         <v>184.14268594001655</v>
       </c>
-      <c r="M51" s="3">
+      <c r="M51" s="2">
         <v>1438.337103544776</v>
       </c>
-      <c r="N51" s="3">
+      <c r="N51" s="2">
         <v>13.468656716417911</v>
       </c>
-      <c r="O51" s="3">
+      <c r="O51" s="2">
         <v>20</v>
       </c>
-      <c r="P51" s="3">
+      <c r="P51" s="2">
         <v>1.26359806843658</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="Q51" s="2">
         <v>182.87908478281392</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="2">
         <v>0.21032780880733573</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="2">
         <v>7.1985386138651818E-3</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="2">
         <v>0.60226469164464014</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="2">
         <v>38.600686554177116</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="2">
         <v>0.70513302952293866</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="2">
         <v>0.53814542742041471</v>
       </c>
-      <c r="I53" s="3">
+      <c r="I53" s="2">
         <v>0.77611940298507465</v>
       </c>
-      <c r="J53" s="3">
+      <c r="J53" s="2">
         <v>0.90049751243781095</v>
       </c>
-      <c r="K53" s="3">
+      <c r="K53" s="2">
         <v>0.63485074626865667</v>
       </c>
-      <c r="L53" s="3">
+      <c r="L53" s="2">
         <v>63.179641463863312</v>
       </c>
-      <c r="M53" s="3">
+      <c r="M53" s="2">
         <v>1400.752740205224</v>
       </c>
-      <c r="N53" s="3">
+      <c r="N53" s="2">
         <v>12.843283582089549</v>
       </c>
-      <c r="O53" s="3">
+      <c r="O53" s="2">
         <v>3.4925373134328357</v>
       </c>
-      <c r="P53" s="3">
+      <c r="P53" s="2">
         <v>0.39747077315600948</v>
       </c>
-      <c r="Q53" s="3">
+      <c r="Q53" s="2">
         <v>46.146305176749159</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="5"/>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="3">
-        <v>0.17272967733339642</v>
-      </c>
-      <c r="D54" s="3">
-        <v>3.3192510036021868E-3</v>
-      </c>
-      <c r="E54" s="3">
-        <v>0.56513352714367771</v>
-      </c>
-      <c r="F54" s="3">
-        <v>36.794409720947847</v>
-      </c>
-      <c r="G54" s="3">
-        <v>0.58668787296047109</v>
-      </c>
-      <c r="H54" s="3">
-        <v>0.42949316649700181</v>
-      </c>
-      <c r="I54" s="3">
-        <v>0.71641791044776115</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0.83768656716417911</v>
-      </c>
-      <c r="K54" s="3">
-        <v>0.56740298507462683</v>
-      </c>
-      <c r="L54" s="3">
-        <v>28.834370933361907</v>
-      </c>
-      <c r="M54" s="3">
-        <v>1407.798973880597</v>
-      </c>
-      <c r="N54" s="3">
-        <v>12.976119402985068</v>
-      </c>
-      <c r="O54" s="3">
-        <v>3.2537313432835822</v>
-      </c>
-      <c r="P54" s="3">
-        <v>0.38214589944526328</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>12.659667933165137</v>
+      <c r="C54" s="2">
+        <v>0.19005807053118712</v>
+      </c>
+      <c r="D54" s="2">
+        <v>4.9212535919841175E-3</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0.58346998825002072</v>
+      </c>
+      <c r="F54" s="2">
+        <v>39.494106218123186</v>
+      </c>
+      <c r="G54" s="2">
+        <v>0.6288165572589729</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0.43035505246874867</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0.73134328358208955</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.89738805970149249</v>
+      </c>
+      <c r="K54" s="2">
+        <v>0.84552238805970148</v>
+      </c>
+      <c r="L54" s="2">
+        <v>31.202868091526316</v>
+      </c>
+      <c r="M54" s="2">
+        <v>1409.2986240671642</v>
+      </c>
+      <c r="N54" s="2">
+        <v>13.002985074626869</v>
+      </c>
+      <c r="O54" s="2">
+        <v>3.3731343283582089</v>
+      </c>
+      <c r="P54" s="2">
+        <v>0.38512414249021615</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>12.73401995559237</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="5"/>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="2">
         <v>0.19347961587081355</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="2">
         <v>4.9147067780128915E-3</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="2">
         <v>0.57557768652688213</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="2">
         <v>31.724875950856546</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="2">
         <v>0.92270814022920011</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55" s="2">
         <v>0.43459149793364937</v>
       </c>
-      <c r="I55" s="3">
+      <c r="I55" s="2">
         <v>0.64179104477611937</v>
       </c>
-      <c r="J55" s="3">
+      <c r="J55" s="2">
         <v>0.69589552238805974</v>
       </c>
-      <c r="K55" s="3">
+      <c r="K55" s="2">
         <v>0.61820895522388064</v>
       </c>
-      <c r="L55" s="3">
+      <c r="L55" s="2">
         <v>85.82678962821393</v>
       </c>
-      <c r="M55" s="3">
+      <c r="M55" s="2">
         <v>1396.5927005597016</v>
       </c>
-      <c r="N55" s="3">
+      <c r="N55" s="2">
         <v>12.264179104477609</v>
       </c>
-      <c r="O55" s="3">
+      <c r="O55" s="2">
         <v>3.2238805970149254</v>
       </c>
-      <c r="P55" s="3">
+      <c r="P55" s="2">
         <v>0.31963275083855019</v>
       </c>
-      <c r="Q55" s="3">
+      <c r="Q55" s="2">
         <v>55.839188863982024</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="5"/>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="2">
         <v>0.20648831470444742</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="2">
         <v>9.9621512681565116E-3</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="2">
         <v>0.58991258268925684</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56" s="2">
         <v>40.338919972109274</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="2">
         <v>0.87804204110132555</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56" s="2">
         <v>0.48424450012812376</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56" s="2">
         <v>0.46268656716417911</v>
       </c>
-      <c r="J56" s="3">
+      <c r="J56" s="2">
         <v>0.56902985074626866</v>
       </c>
-      <c r="K56" s="3">
+      <c r="K56" s="2">
         <v>0.60970149253731343</v>
       </c>
-      <c r="L56" s="3">
+      <c r="L56" s="2">
         <v>154.33254678569622</v>
       </c>
-      <c r="M56" s="3">
+      <c r="M56" s="2">
         <v>1424.7369402985075</v>
       </c>
-      <c r="N56" s="3">
+      <c r="N56" s="2">
         <v>13.126865671641795</v>
       </c>
-      <c r="O56" s="3">
+      <c r="O56" s="2">
         <v>3.4626865671641789</v>
       </c>
-      <c r="P56" s="3">
+      <c r="P56" s="2">
         <v>1.8163108434250106</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="Q56" s="2">
         <v>17.081727383741693</v>
       </c>
     </row>
@@ -2606,4 +2618,1031 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6304186-86E8-C149-86CD-44CE6D38CC95}">
+  <dimension ref="C7:S22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="7" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C7" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.17187122778704217</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1.6823359327930115E-3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.53625104943318158</v>
+      </c>
+      <c r="H9" s="2">
+        <v>33.017458358980285</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1.2965315430118054</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.36585734129401243</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0.52238805970149249</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="2">
+        <v>6.5443769141809263</v>
+      </c>
+      <c r="O9" s="2">
+        <v>1676.9828591417911</v>
+      </c>
+      <c r="P9" s="2">
+        <v>10.508955223880601</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
+        <v>6.5443749392210551</v>
+      </c>
+    </row>
+    <row r="10" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C10" s="5"/>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.17801849367442651</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2.5685541088484817E-3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.54878822680729533</v>
+      </c>
+      <c r="H10" s="2">
+        <v>32.842687163703374</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1.4169761380514467</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.44444235405605026</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0.53731343283582089</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.73484848484848486</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="N10" s="2">
+        <v>9.075428215425406</v>
+      </c>
+      <c r="O10" s="2">
+        <v>2145.71484375</v>
+      </c>
+      <c r="P10" s="2">
+        <v>10.620895522388061</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>9.0754260376318179</v>
+      </c>
+    </row>
+    <row r="11" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C11" s="5"/>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6.393939405995154E-2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1.1433550834854814E-80</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.37233568816932278</v>
+      </c>
+      <c r="H11" s="2">
+        <v>41.504495545278353</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.59577970437119787</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.5991471215351813E-2</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0.13432835820895522</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.45614035087719296</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="N11" s="2">
+        <v>31.539145391378831</v>
+      </c>
+      <c r="O11" s="2">
+        <v>2180.40234375</v>
+      </c>
+      <c r="P11" s="2">
+        <v>10.561194029850748</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>5</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>31.539142669136844</v>
+      </c>
+    </row>
+    <row r="12" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C12" s="5"/>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6.2242148159929879E-2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>5.7848736720451813E-4</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.36754202531344854</v>
+      </c>
+      <c r="H12" s="2">
+        <v>30.597357698410029</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0.55069848681965272</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5.3980099502487562E-2</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.16417910447761194</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0.44642857142857145</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>50.368515954088807</v>
+      </c>
+      <c r="O12" s="2">
+        <v>2180.3982042910447</v>
+      </c>
+      <c r="P12" s="2">
+        <v>10.632835820895526</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>19.985074626865671</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>50.368513292341092</v>
+      </c>
+    </row>
+    <row r="13" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+    </row>
+    <row r="14" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2">
+        <v>7.4357338638124423E-2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2.8599389235983896E-80</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.40856845765861111</v>
+      </c>
+      <c r="H14" s="2">
+        <v>42.375282118241429</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.78333346135989057</v>
+      </c>
+      <c r="J14" s="2">
+        <v>6.3868159203980104E-2</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0.20895522388059701</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.515625</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0.62313432835820892</v>
+      </c>
+      <c r="N14" s="2">
+        <v>15.75743283442597</v>
+      </c>
+      <c r="O14" s="2">
+        <v>1981.6038945895523</v>
+      </c>
+      <c r="P14" s="2">
+        <v>10.317910447761193</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0.29235350907738528</v>
+      </c>
+      <c r="S14" s="2">
+        <v>15.757432830000001</v>
+      </c>
+    </row>
+    <row r="15" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C15" s="5"/>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="2">
+        <v>6.0056694885999795E-2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3.7402823509720762E-5</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0.40375139997966253</v>
+      </c>
+      <c r="H15" s="2">
+        <v>54.251200854475535</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.60507362844870649</v>
+      </c>
+      <c r="J15" s="2">
+        <v>5.9914712153518124E-2</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0.14925373134328357</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0.47692307692307695</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0.80820895522388059</v>
+      </c>
+      <c r="N15" s="2">
+        <v>15.530315221245608</v>
+      </c>
+      <c r="O15" s="2">
+        <v>1365.955865205224</v>
+      </c>
+      <c r="P15" s="2">
+        <v>10.994029850746266</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="R15" s="2">
+        <v>0.11806695141009431</v>
+      </c>
+      <c r="S15" s="2">
+        <v>15.41224577533665</v>
+      </c>
+    </row>
+    <row r="16" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C16" s="5"/>
+      <c r="D16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.1233510643546198</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.2355006219312719E-3</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.47611352489955389</v>
+      </c>
+      <c r="H16" s="2">
+        <v>29.787574661182045</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1.5859703495953432</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0.25565442142483413</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0.40298507462686567</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1.7992537313432835</v>
+      </c>
+      <c r="N16" s="2">
+        <v>43.254507648411085</v>
+      </c>
+      <c r="O16" s="2">
+        <v>2260.4869986007461</v>
+      </c>
+      <c r="P16" s="2">
+        <v>10.47313432835821</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>5</v>
+      </c>
+      <c r="R16" s="2">
+        <v>0.31781011552953009</v>
+      </c>
+      <c r="S16" s="2">
+        <v>42.936694746586817</v>
+      </c>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C17" s="5"/>
+      <c r="D17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="2">
+        <v>8.1073729927789204E-2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1.571567766309332E-80</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.42060439177413483</v>
+      </c>
+      <c r="H17" s="2">
+        <v>41.726882280440613</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.58251703380657316</v>
+      </c>
+      <c r="J17" s="2">
+        <v>4.3319118692253022E-2</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0.14925373134328357</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0.64350746268656711</v>
+      </c>
+      <c r="N17" s="2">
+        <v>76.351359296200883</v>
+      </c>
+      <c r="O17" s="2">
+        <v>2203.453125</v>
+      </c>
+      <c r="P17" s="2">
+        <v>10.374626865671637</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>19.671641791044777</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0.69744205830702144</v>
+      </c>
+      <c r="S17" s="2">
+        <v>75.653914181154164</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.18353222761234828</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1.7122495972315774E-3</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.55960627456209555</v>
+      </c>
+      <c r="H19" s="2">
+        <v>27.318773876372692</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.97568072988664178</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.49396904028101751</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.5074626865671642</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0.65671641791044777</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0.58283582089552233</v>
+      </c>
+      <c r="N19" s="2">
+        <v>37.424903595625466</v>
+      </c>
+      <c r="O19" s="2">
+        <v>1946.1343866604477</v>
+      </c>
+      <c r="P19" s="2">
+        <v>9.8611940298507452</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>3.4029850746268657</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1.6870921263054235</v>
+      </c>
+      <c r="S19" s="2">
+        <v>24.93746585632438</v>
+      </c>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C20" s="5"/>
+      <c r="D20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="2">
+        <v>8.5884344168582261E-2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>5.936586581684919E-5</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.4180413715874971</v>
+      </c>
+      <c r="H20" s="2">
+        <v>33.967473243603955</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.94675389136477706</v>
+      </c>
+      <c r="J20" s="2">
+        <v>6.7501776830135043E-2</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.19402985074626866</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0.50403225806451613</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0.63805970149253732</v>
+      </c>
+      <c r="N20" s="2">
+        <v>25.561154290811338</v>
+      </c>
+      <c r="O20" s="2">
+        <v>2120.96875</v>
+      </c>
+      <c r="P20" s="2">
+        <v>9.6417910447761201</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>3.5223880597014925</v>
+      </c>
+      <c r="R20" s="2">
+        <v>1.9421251033669087</v>
+      </c>
+      <c r="S20" s="2">
+        <v>11.508546096175465</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>7.9005577236416213E-2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1.7117909315242128E-80</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.38339155556550669</v>
+      </c>
+      <c r="H21" s="2">
+        <v>32.912814419268088</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0.87750061645277477</v>
+      </c>
+      <c r="J21" s="2">
+        <v>4.4527363184079606E-2</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0.17910447761194029</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0.60149253731343277</v>
+      </c>
+      <c r="N21" s="2">
+        <v>44.033866451747379</v>
+      </c>
+      <c r="O21" s="2">
+        <v>2164.8579174440297</v>
+      </c>
+      <c r="P21" s="2">
+        <v>10.38208955223881</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>3.5522388059701493</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0.60724402185696269</v>
+      </c>
+      <c r="S21" s="2">
+        <v>9.9746443905047517</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="C22" s="5"/>
+      <c r="D22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="2">
+        <v>7.2651468633059546E-2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1.7821950214249403E-4</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.37483565709484157</v>
+      </c>
+      <c r="H22" s="2">
+        <v>31.86824809127102</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0.58580871747687857</v>
+      </c>
+      <c r="J22" s="2">
+        <v>3.4825870646766163E-2</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.14925373134328357</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0.48214285714285715</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0.57164179104477608</v>
+      </c>
+      <c r="N22" s="2">
+        <v>72.780948670942394</v>
+      </c>
+      <c r="O22" s="2">
+        <v>2149.73046875</v>
+      </c>
+      <c r="P22" s="2">
+        <v>10.329850746268658</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>3.6716417910447761</v>
+      </c>
+      <c r="R22" s="2">
+        <v>1.4789056493275201</v>
+      </c>
+      <c r="S22" s="2">
+        <v>7.0157200222584741</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="C19:C22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C584F198-0FE1-8845-A633-0DEF80854601}">
+  <dimension ref="C12:R23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="12" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="D12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="2">
+        <v>6.545635018463597E-2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1.1133412201131752E-3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.39599833670836776</v>
+      </c>
+      <c r="G13" s="2">
+        <v>16.636197735410072</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.73919516882870817</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.17542487144111377</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.38805970149253732</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.60895522388059697</v>
+      </c>
+      <c r="M13" s="2">
+        <v>32.887150938831155</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1122.8927821828358</v>
+      </c>
+      <c r="O13" s="2">
+        <v>10.779104477611938</v>
+      </c>
+      <c r="P13" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2">
+        <v>32.887148778830003</v>
+      </c>
+    </row>
+    <row r="14" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14">
+        <v>6.4359140320740096E-2</v>
+      </c>
+      <c r="E14">
+        <v>6.7433027573594981E-4</v>
+      </c>
+      <c r="F14">
+        <v>0.43765674042167946</v>
+      </c>
+      <c r="G14">
+        <v>56.1713740072382</v>
+      </c>
+      <c r="H14">
+        <v>0.86771694692721235</v>
+      </c>
+      <c r="I14">
+        <v>0.10024875621890546</v>
+      </c>
+      <c r="J14">
+        <v>0.19402985074626866</v>
+      </c>
+      <c r="K14">
+        <v>0.47761194029850745</v>
+      </c>
+      <c r="L14">
+        <v>0.51517412935323381</v>
+      </c>
+      <c r="M14">
+        <v>12.547144968118241</v>
+      </c>
+      <c r="N14">
+        <v>1087.5989972014925</v>
+      </c>
+      <c r="O14">
+        <v>11.505970149253733</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>12.547143114146902</v>
+      </c>
+    </row>
+    <row r="15" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15">
+        <v>0.10887106917037502</v>
+      </c>
+      <c r="E15">
+        <v>5.8409831720597786E-4</v>
+      </c>
+      <c r="F15">
+        <v>0.50454291212024971</v>
+      </c>
+      <c r="G15">
+        <v>35.699222830410498</v>
+      </c>
+      <c r="H15">
+        <v>5.5133439772955581</v>
+      </c>
+      <c r="I15">
+        <v>0.2351066003063369</v>
+      </c>
+      <c r="J15">
+        <v>0.34328358208955223</v>
+      </c>
+      <c r="K15">
+        <v>0.59888059701492535</v>
+      </c>
+      <c r="L15">
+        <v>0.8</v>
+      </c>
+      <c r="M15">
+        <v>72.249147404485669</v>
+      </c>
+      <c r="N15">
+        <v>1124.1605643656717</v>
+      </c>
+      <c r="O15">
+        <v>11.402985074626866</v>
+      </c>
+      <c r="P15">
+        <v>5</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>72.249145027416859</v>
+      </c>
+    </row>
+    <row r="16" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>3.2366258613803003E-2</v>
+      </c>
+      <c r="E16">
+        <v>3.863700800493757E-5</v>
+      </c>
+      <c r="F16">
+        <v>0.31777023735331067</v>
+      </c>
+      <c r="G16">
+        <v>18.796328645593785</v>
+      </c>
+      <c r="H16">
+        <v>0.64484053375843819</v>
+      </c>
+      <c r="I16">
+        <v>3.3582089552238806E-2</v>
+      </c>
+      <c r="J16">
+        <v>0.16417910447761194</v>
+      </c>
+      <c r="K16">
+        <v>0.44711538461538464</v>
+      </c>
+      <c r="L16">
+        <v>0.55567164179104489</v>
+      </c>
+      <c r="M16">
+        <v>101.17893225755265</v>
+      </c>
+      <c r="N16">
+        <v>1075.634911380597</v>
+      </c>
+      <c r="O16">
+        <v>11.229850746268662</v>
+      </c>
+      <c r="P16">
+        <v>19.970149253731343</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>101.17893029326824</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19">
+        <v>6.7803869353453936E-2</v>
+      </c>
+      <c r="E19">
+        <v>4.070790554585057E-4</v>
+      </c>
+      <c r="F19">
+        <v>0.42696540902799635</v>
+      </c>
+      <c r="G19">
+        <v>52.381051688795914</v>
+      </c>
+      <c r="H19">
+        <v>0.86457838519625596</v>
+      </c>
+      <c r="I19">
+        <v>8.9054726368159212E-2</v>
+      </c>
+      <c r="J19">
+        <v>0.17910447761194029</v>
+      </c>
+      <c r="K19">
+        <v>0.47692307692307695</v>
+      </c>
+      <c r="L19">
+        <v>0.87611940298507451</v>
+      </c>
+      <c r="M19">
+        <v>58.184971784477803</v>
+      </c>
+      <c r="N19">
+        <v>1367.4007695895523</v>
+      </c>
+      <c r="O19">
+        <v>11.173134328358206</v>
+      </c>
+      <c r="P19">
+        <v>5</v>
+      </c>
+      <c r="Q19">
+        <v>0.14740811888851338</v>
+      </c>
+      <c r="R19">
+        <v>58.037561128388589</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23">
+        <v>58.21</v>
+      </c>
+      <c r="E23">
+        <v>67</v>
+      </c>
+      <c r="F23">
+        <v>6.7799999999999999E-2</v>
+      </c>
+      <c r="G23">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="H23">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="L23">
+        <v>0.87609999999999999</v>
+      </c>
+      <c r="M23">
+        <v>79.691770930788408</v>
+      </c>
+      <c r="N23">
+        <v>1371.118120335821</v>
+      </c>
+      <c r="O23">
+        <v>11.071641791044781</v>
+      </c>
+      <c r="P23">
+        <v>3.4029850746268657</v>
+      </c>
+      <c r="Q23">
+        <v>0.30057912442221568</v>
+      </c>
+      <c r="R23">
+        <v>52.221939446321173</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>